--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_363_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_363_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,16 +1531,16 @@
         <v>20</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1727,7 +1727,7 @@
         <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
@@ -2315,16 +2315,16 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>3</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
         <v>5</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4292,7 +4292,7 @@
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>6</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>3</v>
@@ -6588,16 +6588,16 @@
         <v>118</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_363_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_363_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -854,17 +854,17 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
         <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>3</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
@@ -5527,11 +5527,11 @@
         <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5676,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y43" t="n">
         <v>3</v>
       </c>
-      <c r="Y43" t="n">
-        <v>4</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y47" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6636,22 +6636,22 @@
         <v>1</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AJ47" t="n">
         <v>10</v>
       </c>
       <c r="AK47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
